--- a/2026/Q3/humanus_board-finance-workbook_Q3-2026.xlsx
+++ b/2026/Q3/humanus_board-finance-workbook_Q3-2026.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,6 +133,7 @@
     <xf numFmtId="166" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -658,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A6:B13"/>
+  <dimension ref="A6:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -724,22 +725,10 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Prepared by</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Stacy McGill, Finance Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Stichting hūmānus international · KvK 77641981 · [TBD: registered-charity footer boilerplate] · Confidential — board use only</t>
         </is>
@@ -1824,7 +1813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1832,7 +1821,8 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1872,10 +1862,15 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
+          <t>Transfers</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -1898,13 +1893,16 @@
       <c r="D5" s="10" t="n">
         <v>203699.5</v>
       </c>
-      <c r="E5" s="10">
-        <f>C5-D5</f>
-        <v/>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Year-2 tranche received Jan 2026</t>
+      <c r="E5" s="10" t="n">
+        <v>-45660.09</v>
+      </c>
+      <c r="F5" s="10">
+        <f>C5-D5+E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Year-2 tranche received Jan 2026; transfer = planned SDC co-funding</t>
         </is>
       </c>
     </row>
@@ -1925,11 +1923,14 @@
       <c r="D6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="10">
-        <f>C6-D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="E6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10">
+        <f>C6-D6+E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1948,11 +1949,14 @@
       <c r="D7" s="10" t="n">
         <v>235.04</v>
       </c>
-      <c r="E7" s="10">
-        <f>C7-D7</f>
-        <v/>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <f>C7-D7+E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>non-cash</t>
         </is>
@@ -1975,11 +1979,14 @@
       <c r="D8" s="10" t="n">
         <v>42.38</v>
       </c>
-      <c r="E8" s="10">
-        <f>C8-D8</f>
-        <v/>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <f>C8-D8+E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>OSF #1 9.36 + untagged 33.02</t>
         </is>
@@ -2002,13 +2009,16 @@
       <c r="D9" s="10" t="n">
         <v>52872.1</v>
       </c>
-      <c r="E9" s="10">
-        <f>C9-D9</f>
-        <v/>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>2026 receipts also fund 2025 spend of 8,132.90 — lifetime nil</t>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10">
+        <f>C9-D9+E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2026 receipts also fund 2025 spend of 8,132.90 — balanced over grant life</t>
         </is>
       </c>
     </row>
@@ -2029,13 +2039,16 @@
       <c r="D10" s="10" t="n">
         <v>43847.67</v>
       </c>
-      <c r="E10" s="10">
-        <f>C10-D10</f>
-        <v/>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>reimbursement grant — claim not yet invoiced</t>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
+        <f>C10-D10+E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>reimbursement grant — timing only; claim due 16 Oct</t>
         </is>
       </c>
     </row>
@@ -2056,13 +2069,16 @@
       <c r="D11" s="10" t="n">
         <v>73790.56</v>
       </c>
-      <c r="E11" s="10">
-        <f>C11-D11</f>
-        <v/>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>final instalment; Art. 1.2 50% co-funding falls on core</t>
+      <c r="E11" s="10" t="n">
+        <v>45660.09</v>
+      </c>
+      <c r="F11" s="10">
+        <f>C11-D11+E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>final instalment + hūmānus' planned matched share (Art. 1.2); balanced and audited</t>
         </is>
       </c>
     </row>
@@ -2083,13 +2099,16 @@
       <c r="D12" s="10" t="n">
         <v>27410</v>
       </c>
-      <c r="E12" s="10">
-        <f>C12-D12</f>
-        <v/>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>tranche 2 due 31 Jan 2027</t>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10">
+        <f>C12-D12+E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>timing only; tranche 2 due 31 Jan 2027</t>
         </is>
       </c>
     </row>
@@ -2100,19 +2119,23 @@
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr"/>
-      <c r="C13" s="11">
+      <c r="C13" s="14">
         <f>SUM(C5:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="14">
         <f>SUM(D5:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="14">
         <f>SUM(E5:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="F13" s="14">
+        <f>SUM(F5:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3279,31 +3302,31 @@
           <t>Executive Director</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="15" t="n">
         <v>14200</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="15" t="n">
         <v>14200</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>14200</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>14200</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="15" t="n">
         <v>14200</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="15" t="n">
         <v>14200</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="H5" s="15" t="n">
         <v>14200</v>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="I5" s="15" t="n">
         <v>14200</v>
       </c>
-      <c r="J5" s="14" t="n">
+      <c r="J5" s="15" t="n">
         <v>14200</v>
       </c>
     </row>
@@ -3313,31 +3336,31 @@
           <t>Communication Advisor</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="15" t="n">
         <v>5383.27</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="15" t="n">
         <v>5383.27</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>5383.27</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>5383.27</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="15" t="n">
         <v>5383.27</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="15" t="n">
         <v>5383.27</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="15" t="n">
         <v>5383.27</v>
       </c>
-      <c r="I6" s="14" t="n">
+      <c r="I6" s="15" t="n">
         <v>5383.27</v>
       </c>
-      <c r="J6" s="14" t="n">
+      <c r="J6" s="15" t="n">
         <v>5383.27</v>
       </c>
     </row>
@@ -3347,31 +3370,31 @@
           <t>Advocate / Programme Manager</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>3500</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="J7" s="15" t="n">
         <v>3500</v>
       </c>
     </row>
@@ -3381,31 +3404,31 @@
           <t>Rohingya Manager (cash)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>2435.03</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>2500</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="15" t="n">
         <v>2500</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="15" t="n">
         <v>2500</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="15" t="n">
         <v>2500</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="15" t="n">
         <v>2500</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3415,31 +3438,31 @@
           <t>Cost of Living Allowance (GBP 1,400)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="15" t="n">
         <v>1856.12</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="15" t="n">
         <v>1856.12</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>1856.12</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <v>1856.12</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <v>1856.12</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="15" t="n">
         <v>1856.12</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="15" t="n">
         <v>1856.12</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I9" s="15" t="n">
         <v>1856.12</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="15" t="n">
         <v>1856.12</v>
       </c>
     </row>
@@ -3449,31 +3472,31 @@
           <t>Finance Manager (SK Das)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="15" t="n">
         <v>2000</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="I10" s="14" t="n">
+      <c r="I10" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="J10" s="14" t="n">
+      <c r="J10" s="15" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3483,31 +3506,31 @@
           <t>Communication Support</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="15" t="n">
         <v>649.41</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="15" t="n">
         <v>649.41</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>649.41</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <v>649.41</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="15" t="n">
         <v>649.41</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="15" t="n">
         <v>649.41</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="15" t="n">
         <v>649.41</v>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="I11" s="15" t="n">
         <v>649.41</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="15" t="n">
         <v>649.41</v>
       </c>
     </row>
@@ -3517,31 +3540,31 @@
           <t>IT &amp; software</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="15" t="n">
         <v>352.7</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="15" t="n">
         <v>352.7</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>352.7</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <v>352.7</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="15" t="n">
         <v>352.7</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="15" t="n">
         <v>352.7</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="15" t="n">
         <v>352.7</v>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="I12" s="15" t="n">
         <v>352.7</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="15" t="n">
         <v>352.7</v>
       </c>
     </row>
@@ -3551,31 +3574,31 @@
           <t>Bank charges</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="15" t="n">
         <v>55.74</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="15" t="n">
         <v>55.74</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>55.74</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="15" t="n">
         <v>55.74</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="15" t="n">
         <v>55.74</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="15" t="n">
         <v>55.74</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="15" t="n">
         <v>55.74</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="I13" s="15" t="n">
         <v>55.74</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="15" t="n">
         <v>55.74</v>
       </c>
     </row>
@@ -3585,31 +3608,31 @@
           <t>One-off committed bills</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="15" t="n">
         <v>5282.7</v>
       </c>
-      <c r="C14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="14" t="n">
+      <c r="C14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="15" t="n">
         <v>3000</v>
       </c>
-      <c r="I14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="14" t="n">
+      <c r="I14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3619,10 +3642,10 @@
           <t>Programme &amp; travel per month — selected scenario</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="16" t="n">
         <v>5000</v>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Central 5,000 · Freeze 0 · Q3 run-rate 10,636</t>
         </is>
@@ -3686,31 +3709,31 @@
           <t>FCDO Phase II claim Jun–Oct 2026 (Schedule 2, ind. Nov 2026)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="14" t="n">
+      <c r="B19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="15" t="n">
         <v>52800</v>
       </c>
-      <c r="D19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="14" t="n">
+      <c r="D19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3720,31 +3743,31 @@
           <t>OSF #4 Year-3 tranche (contract: January 2027)</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="14" t="n">
+      <c r="B20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15" t="n">
         <v>300000</v>
       </c>
-      <c r="F20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="14" t="n">
+      <c r="F20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3754,31 +3777,31 @@
           <t>Swiss Myanmar tranche 2 (§3.3: 31 Jan 2027)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="14" t="n">
+      <c r="B21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15" t="n">
         <v>24946.67</v>
       </c>
-      <c r="F21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="14" t="n">
+      <c r="F21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3788,31 +3811,31 @@
           <t>FCDO Phase II final claim Nov 26–Mar 27 (ind. May 2027)</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="14" t="n">
+      <c r="B22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15" t="n">
         <v>47000</v>
       </c>
-      <c r="J22" s="14" t="n">
+      <c r="J22" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3822,31 +3845,31 @@
           <t>Swiss Myanmar tranche 3 (§3.3: 30 Jun 2027)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="14" t="n">
+      <c r="B23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="15" t="n">
         <v>24946.66</v>
       </c>
     </row>
@@ -3955,38 +3978,38 @@
           <t>Opening cash</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>33679.3</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <f>B24</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <f>C24</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <f>D24</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="18">
         <f>E24</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>F24</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="18">
         <f>G24</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="18">
         <f>H24</f>
         <v/>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="18">
         <f>I24</f>
         <v/>
       </c>
@@ -4766,44 +4789,44 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Closing cash</t>
         </is>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="20">
         <f>B5+B23-B17</f>
         <v/>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="20">
         <f>C5+C23-C17</f>
         <v/>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <f>D5+D23-D17</f>
         <v/>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <f>E5+E23-E17</f>
         <v/>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="20">
         <f>F5+F23-F17</f>
         <v/>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="20">
         <f>G5+G23-G17</f>
         <v/>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="20">
         <f>H5+H23-H17</f>
         <v/>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="20">
         <f>I5+I23-I17</f>
         <v/>
       </c>
-      <c r="J24" s="19">
+      <c r="J24" s="20">
         <f>J5+J23-J17</f>
         <v/>
       </c>
@@ -5126,16 +5149,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5160,30 +5182,25 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Clause</t>
+          <t>Due</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Due</t>
+          <t>Amount (contract ccy)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Amount (contract ccy)</t>
+          <t>Xero ref</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Xero ref</t>
+          <t>Received (USD)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Received (USD)</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -5192,96 +5209,82 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>OSF #4 Y1</t>
+          <t>OSF #4 Y2</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Award p.1</t>
+          <t>Jan 2026</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Dec 2024</t>
+          <t>USD 300,000.00</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>USD 300,000.00</t>
+          <t>bank 22 Jan 26</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2024 receipt</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>300,000</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>PAID 2024</t>
+          <t>PAID</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>OSF #4 Y2</t>
+          <t>FCDO II claim 1</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Award p.1</t>
+          <t>16 Oct report → ind. Nov 2026</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>GBP — reported expenses</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>USD 300,000.00</t>
+          <t>USD 54,017</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>bank 22 Jan 26</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>300,000</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>OSF #4 Y3</t>
+          <t>FCDO II claim 2</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Award p.1</t>
+          <t>30 Apr 2027 → ind. May 2027</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Jan 2027</t>
+          <t>GBP — reported expenses</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>USD 300,000.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5291,108 +5294,93 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Not yet due — ask for early release (D2)</t>
+          <t>Within £80,884.70 ceiling (cl. 6.1)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>OSF #4 Y4–Y5</t>
+          <t>Swiss Myanmar T1</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Award p.1</t>
+          <t>30 Jun 2026</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Jan 2028 / Jan 2029</t>
+          <t>USD 24,946.67</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>USD 600,000.00</t>
+          <t>INV-0010</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24,946.00</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Future</t>
+          <t>PAID 10 Jul</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>FCDO II claim 1</t>
+          <t>Swiss Myanmar T2</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Sched. 2</t>
+          <t>31 Jan 2027</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>16 Oct report → ind. Nov 2026</t>
+          <t>USD 24,946.67</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>GBP — reported expenses</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>INV-0012 DRAFT USD 54,017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Re-state in GBP (cl. 6.4); about USD 52,800 supportable</t>
+          <t>Gated: invoice + FDFA funds; Stimson indicated Dec 2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>FCDO II claim 2</t>
+          <t>Swiss Myanmar T3</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sched. 2</t>
+          <t>30 Jun 2027</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>30 Apr 2027 → ind. May 2027</t>
+          <t>USD 24,946.66</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>GBP — reported expenses</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -5402,160 +5390,39 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Within £80,884.70 ceiling (cl. 6.1)</t>
+          <t>Gated as T2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Swiss Myanmar T1</t>
+          <t>SDC (closed) T1–T3</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>§3.3</t>
+          <t>Nov 24 / Aug 25 / after final report</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>30 Jun 2026</t>
+          <t>CHF 182,788.10</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>USD 24,946.67</t>
+          <t>INV-0005/6/11</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>INV-0010</t>
+          <t>221,668.08</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>24,946.00</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>PAID 10 Jul (0.67 short)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Swiss Myanmar T2</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>§3.3</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>31 Jan 2027</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>USD 24,946.67</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Gated: invoice + FDFA funds; Stimson indicated Dec 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Swiss Myanmar T3</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>§3.3</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>30 Jun 2027</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>USD 24,946.66</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Gated as T2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>SDC (closed) T1–T3</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Art. 4.1</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Nov 24 / Aug 25 / after final report</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>CHF 182,788.10</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>INV-0005/6/11</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>221,668.08</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>FULLY DRAWN — Art. 1.1 cap</t>
+          <t>FULLY DRAWN</t>
         </is>
       </c>
     </row>
